--- a/Backtest/09-07-21/S&P500stock_09-07-21period252RS90.xlsx
+++ b/Backtest/09-07-21/S&P500stock_09-07-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="81">
   <si>
     <t>Stock</t>
   </si>
@@ -130,109 +130,133 @@
     <t>MRNA</t>
   </si>
   <si>
-    <t>F</t>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>STLD</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>ALB</t>
   </si>
   <si>
     <t>GNRC</t>
   </si>
   <si>
-    <t>DVN</t>
-  </si>
-  <si>
-    <t>OKE</t>
-  </si>
-  <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
     <t>ZBRA</t>
   </si>
   <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>HCA</t>
-  </si>
-  <si>
-    <t>TRGP</t>
-  </si>
-  <si>
-    <t>DECK</t>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>AVY</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>EPAM</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>2021-08-05</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
+    <t>2021-11-04</t>
+  </si>
+  <si>
+    <t>2021-10-21</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>2021-11-01</t>
+  </si>
+  <si>
+    <t>2021-11-03</t>
+  </si>
+  <si>
+    <t>2021-10-22</t>
+  </si>
+  <si>
+    <t>2021-10-27</t>
+  </si>
+  <si>
+    <t>2021-10-14</t>
   </si>
   <si>
     <t>Healthcare</t>
   </si>
   <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
     <t>Biotechnology</t>
   </si>
   <si>
-    <t>Auto Manufacturers</t>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Information Technology Services</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Specialty Chemicals</t>
   </si>
   <si>
     <t>Specialty Industrial Machinery</t>
   </si>
   <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
-    <t>Discount Stores</t>
-  </si>
-  <si>
-    <t>Information Technology Services</t>
-  </si>
-  <si>
     <t>Communication Equipment</t>
   </si>
   <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Medical Care Facilities</t>
-  </si>
-  <si>
-    <t>Footwear &amp; Accessories</t>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>Packaging &amp; Containers</t>
   </si>
 </sst>
 </file>
@@ -590,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -714,40 +738,40 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>232.79</v>
+        <v>416.7</v>
       </c>
       <c r="E2">
-        <v>3.36</v>
+        <v>6.6</v>
       </c>
       <c r="F2">
-        <v>1.914660858672649</v>
+        <v>3.152614886408817</v>
       </c>
       <c r="G2">
-        <v>3.65</v>
+        <v>5.17</v>
       </c>
       <c r="H2">
-        <v>1.76795982748572</v>
+        <v>3.07650479331496</v>
       </c>
       <c r="I2">
-        <v>231.4879974365234</v>
+        <v>390.3360046386719</v>
       </c>
       <c r="J2">
-        <v>218.7944999694824</v>
+        <v>398.9845001220703</v>
       </c>
       <c r="K2">
-        <v>192.8625997924805</v>
+        <v>337.1786990356445</v>
       </c>
       <c r="L2">
-        <v>141.063450050354</v>
+        <v>199.9392248916626</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="N2">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -777,43 +801,43 @@
         <v>54.21</v>
       </c>
       <c r="Y2">
-        <v>245.7</v>
+        <v>497.49</v>
       </c>
       <c r="Z2">
-        <v>56.31</v>
+        <v>101.28</v>
       </c>
       <c r="AA2">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="AB2">
-        <v>179.56</v>
+        <v>536.1799999999999</v>
       </c>
       <c r="AC2">
-        <v>1083.87</v>
+        <v>1274.58</v>
       </c>
       <c r="AD2">
-        <v>31.81</v>
+        <v>41.47</v>
       </c>
       <c r="AE2">
+        <v>127.21</v>
+      </c>
+      <c r="AF2">
         <v>529.58</v>
       </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>-20.34</v>
       </c>
-      <c r="AG2">
-        <v>-90.31999999999999</v>
-      </c>
       <c r="AH2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AI2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="AJ2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AK2">
-        <v>82.91401203735748</v>
+        <v>88.55322270971158</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -821,58 +845,58 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>96.16935483870968</v>
+        <v>97.98387096774194</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="D3">
-        <v>14.06</v>
+        <v>114.05</v>
       </c>
       <c r="E3">
-        <v>1.62</v>
+        <v>3.12</v>
       </c>
       <c r="F3">
-        <v>-0.2771219663868305</v>
+        <v>0.8133611967067527</v>
       </c>
       <c r="G3">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="H3">
-        <v>0.7688569482321616</v>
+        <v>0.6268740174466215</v>
       </c>
       <c r="I3">
-        <v>14.52600002288818</v>
+        <v>116.8380004882813</v>
       </c>
       <c r="J3">
-        <v>14.87950000762939</v>
+        <v>119.1809993743896</v>
       </c>
       <c r="K3">
-        <v>13.78219999313355</v>
+        <v>105.9795997619629</v>
       </c>
       <c r="L3">
-        <v>10.95259996891022</v>
+        <v>80.71989992141724</v>
       </c>
       <c r="M3">
         <v>0.98</v>
       </c>
       <c r="N3">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -884,46 +908,46 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>5.74</v>
+        <v>44.05</v>
       </c>
       <c r="Y3">
-        <v>16.45</v>
+        <v>128.81</v>
       </c>
       <c r="Z3">
-        <v>49.2</v>
+        <v>28.54</v>
       </c>
       <c r="AA3">
-        <v>2.76</v>
+        <v>75.95</v>
       </c>
       <c r="AB3">
-        <v>300</v>
+        <v>336.8</v>
       </c>
       <c r="AC3">
-        <v>192.86</v>
+        <v>701.59</v>
       </c>
       <c r="AD3">
-        <v>9.6</v>
+        <v>12.36</v>
       </c>
       <c r="AE3">
-        <v>217.14</v>
+        <v>62.9</v>
       </c>
       <c r="AF3">
-        <v>-216.67</v>
+        <v>136.64</v>
       </c>
       <c r="AG3">
-        <v>114.29</v>
+        <v>107.94</v>
       </c>
       <c r="AH3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AI3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AJ3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="AK3">
-        <v>73.96997904965829</v>
+        <v>83.97618343086783</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -931,64 +955,61 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>99.79838709677419</v>
+        <v>97.58064516129032</v>
       </c>
       <c r="C4">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="D4">
-        <v>426.6</v>
+        <v>313.35</v>
       </c>
       <c r="E4">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="F4">
-        <v>-0.3275077784571634</v>
+        <v>-0.5310374755358135</v>
       </c>
       <c r="G4">
-        <v>2.52</v>
+        <v>1.71</v>
       </c>
       <c r="H4">
-        <v>0.3741496379097685</v>
+        <v>-0.2603938226316742</v>
       </c>
       <c r="I4">
-        <v>423.4660034179688</v>
+        <v>310.0819946289063</v>
       </c>
       <c r="J4">
-        <v>393.9524993896484</v>
+        <v>304.2994979858398</v>
       </c>
       <c r="K4">
-        <v>347.4145983886719</v>
+        <v>277.8155993652344</v>
       </c>
       <c r="L4">
-        <v>281.4669488525391</v>
+        <v>209.8748001098633</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>1.22</v>
-      </c>
-      <c r="O4" t="s">
-        <v>49</v>
+        <v>1.12</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>16.11111111111111</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -997,46 +1018,46 @@
         <v>1</v>
       </c>
       <c r="X4">
-        <v>125.18</v>
+        <v>115.86</v>
       </c>
       <c r="Y4">
-        <v>440</v>
+        <v>317.43</v>
       </c>
       <c r="Z4">
-        <v>20.99</v>
+        <v>20.97</v>
       </c>
       <c r="AA4">
-        <v>83.91</v>
+        <v>17.97</v>
       </c>
       <c r="AB4">
-        <v>44.75</v>
+        <v>128.22</v>
       </c>
       <c r="AC4">
-        <v>129.81</v>
+        <v>1563.16</v>
       </c>
       <c r="AD4">
-        <v>9.84</v>
+        <v>51.41</v>
       </c>
       <c r="AE4">
-        <v>18.32</v>
+        <v>69.89</v>
       </c>
       <c r="AF4">
-        <v>8.6</v>
+        <v>38.81</v>
       </c>
       <c r="AG4">
-        <v>78.84999999999999</v>
+        <v>605.26</v>
       </c>
       <c r="AH4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AI4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="AK4">
-        <v>54.18638686110976</v>
+        <v>75.93561310172269</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1044,43 +1065,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>98.99193548387096</v>
+        <v>95.96774193548387</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="D5">
-        <v>27.76</v>
+        <v>66.77</v>
       </c>
       <c r="E5">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="F5">
-        <v>1.549363721162736</v>
+        <v>0.5646474423418778</v>
       </c>
       <c r="G5">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="H5">
-        <v>1.484263948191499</v>
+        <v>0.5497202922224219</v>
       </c>
       <c r="I5">
-        <v>28.46399993896484</v>
+        <v>67.79199829101563</v>
       </c>
       <c r="J5">
-        <v>28.71700010299683</v>
+        <v>69.19200019836425</v>
       </c>
       <c r="K5">
-        <v>27.48580005645752</v>
+        <v>64.24980018615723</v>
       </c>
       <c r="L5">
-        <v>19.418600025177</v>
+        <v>51.81495006561279</v>
       </c>
       <c r="M5">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="N5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1107,46 +1128,46 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>7.73</v>
+        <v>28.31</v>
       </c>
       <c r="Y5">
-        <v>31.99</v>
+        <v>74.37</v>
       </c>
       <c r="Z5">
-        <v>14.22</v>
+        <v>12.59</v>
       </c>
       <c r="AA5">
-        <v>0.04</v>
+        <v>283.97</v>
       </c>
       <c r="AB5">
-        <v>70.81</v>
+        <v>126.09</v>
       </c>
       <c r="AC5">
-        <v>118.54</v>
+        <v>597.92</v>
       </c>
       <c r="AD5">
-        <v>2.55</v>
+        <v>14.67</v>
       </c>
       <c r="AE5">
-        <v>222.22</v>
+        <v>64.22</v>
       </c>
       <c r="AF5">
-        <v>-8</v>
+        <v>129.21</v>
       </c>
       <c r="AG5">
-        <v>85.95999999999999</v>
+        <v>85.42</v>
       </c>
       <c r="AH5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AI5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AJ5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK5">
-        <v>49.59880337032995</v>
+        <v>67.61272915267394</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1154,43 +1175,43 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>92.13709677419355</v>
+        <v>97.78225806451613</v>
       </c>
       <c r="C6">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="D6">
-        <v>55.38</v>
+        <v>129</v>
       </c>
       <c r="E6">
-        <v>2.03</v>
+        <v>1.23</v>
       </c>
       <c r="F6">
-        <v>0.2393326073340811</v>
+        <v>-0.4570955485624724</v>
       </c>
       <c r="G6">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="H6">
-        <v>-0.6866262585816635</v>
+        <v>-0.4822107826512482</v>
       </c>
       <c r="I6">
-        <v>56.32600021362305</v>
+        <v>126.9960021972656</v>
       </c>
       <c r="J6">
-        <v>55.60399990081787</v>
+        <v>118.3965003967285</v>
       </c>
       <c r="K6">
-        <v>54.32879989624023</v>
+        <v>110.7562002563477</v>
       </c>
       <c r="L6">
-        <v>43.69804996490478</v>
+        <v>84.12435020446777</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1208,55 +1229,55 @@
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>23.28</v>
+        <v>49.26</v>
       </c>
       <c r="Y6">
-        <v>57.5</v>
+        <v>130.78</v>
       </c>
       <c r="Z6">
-        <v>22.64</v>
+        <v>70.06</v>
       </c>
       <c r="AA6">
-        <v>18.42</v>
+        <v>148.48</v>
       </c>
       <c r="AB6">
-        <v>16.89</v>
+        <v>192.86</v>
       </c>
       <c r="AC6">
-        <v>171.88</v>
+        <v>59.65</v>
       </c>
       <c r="AD6">
-        <v>6.33</v>
+        <v>15.46</v>
       </c>
       <c r="AE6">
-        <v>17.57</v>
+        <v>-26.32</v>
       </c>
       <c r="AF6">
-        <v>5.71</v>
+        <v>118.58</v>
       </c>
       <c r="AG6">
-        <v>118.75</v>
+        <v>-0.88</v>
       </c>
       <c r="AH6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AI6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="AJ6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AK6">
-        <v>33.76295937907135</v>
+        <v>55.93081552167168</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1264,43 +1285,43 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>94.15322580645162</v>
+        <v>91.93548387096774</v>
       </c>
       <c r="C7">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="D7">
-        <v>248.58</v>
+        <v>411.31</v>
       </c>
       <c r="E7">
-        <v>0.61</v>
+        <v>1.14</v>
       </c>
       <c r="F7">
-        <v>-1.549363721162736</v>
+        <v>-0.517593488813388</v>
       </c>
       <c r="G7">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="H7">
-        <v>-1.217014206827379</v>
+        <v>-0.4436339200391483</v>
       </c>
       <c r="I7">
-        <v>246.3260009765625</v>
+        <v>413.3160034179688</v>
       </c>
       <c r="J7">
-        <v>238.4205017089844</v>
+        <v>408.5445022583008</v>
       </c>
       <c r="K7">
-        <v>226.5014010620117</v>
+        <v>387.6533996582031</v>
       </c>
       <c r="L7">
-        <v>190.9792010498047</v>
+        <v>333.4430499267578</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1321,52 +1342,52 @@
         <v>1</v>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
       </c>
       <c r="X7">
-        <v>117.06</v>
+        <v>185.52</v>
       </c>
       <c r="Y7">
-        <v>248.96</v>
+        <v>420.76</v>
       </c>
       <c r="Z7">
-        <v>104.33</v>
+        <v>135.11</v>
       </c>
       <c r="AA7">
-        <v>5.69</v>
+        <v>4.47</v>
       </c>
       <c r="AB7">
-        <v>39.86</v>
+        <v>147.92</v>
       </c>
       <c r="AC7">
-        <v>24.26</v>
+        <v>67.81</v>
       </c>
       <c r="AD7">
-        <v>14.02</v>
+        <v>5.92</v>
       </c>
       <c r="AE7">
-        <v>52.73</v>
+        <v>-19.04</v>
       </c>
       <c r="AF7">
-        <v>36.14</v>
+        <v>53.85</v>
       </c>
       <c r="AG7">
-        <v>-40.24</v>
+        <v>34.73</v>
       </c>
       <c r="AH7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AI7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AJ7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="AK7">
-        <v>27.31091959467831</v>
+        <v>53.97622224521879</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1374,43 +1395,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>92.94354838709677</v>
+        <v>94.75806451612904</v>
       </c>
       <c r="C8">
-        <v>397</v>
+        <v>113</v>
       </c>
       <c r="D8">
-        <v>254.23</v>
+        <v>45.71</v>
       </c>
       <c r="E8">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="F8">
-        <v>-0.7935765401077427</v>
+        <v>-0.04033196016727687</v>
       </c>
       <c r="G8">
-        <v>2.13</v>
+        <v>2.51</v>
       </c>
       <c r="H8">
-        <v>-0.1068998965456485</v>
+        <v>0.511143429610322</v>
       </c>
       <c r="I8">
-        <v>253.5519989013672</v>
+        <v>45.08400039672851</v>
       </c>
       <c r="J8">
-        <v>240.9824989318848</v>
+        <v>43.77749996185302</v>
       </c>
       <c r="K8">
-        <v>232.1027993774414</v>
+        <v>40.63459976196289</v>
       </c>
       <c r="L8">
-        <v>178.7567002105713</v>
+        <v>38.01294998168945</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1419,13 +1440,13 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1437,46 +1458,46 @@
         <v>1</v>
       </c>
       <c r="X8">
-        <v>115.86</v>
+        <v>19.75</v>
       </c>
       <c r="Y8">
-        <v>258.31</v>
+        <v>46.4</v>
       </c>
       <c r="Z8">
-        <v>16.27</v>
+        <v>16.98</v>
       </c>
       <c r="AA8">
-        <v>9.279999999999999</v>
+        <v>148.72</v>
       </c>
       <c r="AB8">
-        <v>4.7</v>
+        <v>257.14</v>
       </c>
       <c r="AC8">
-        <v>200</v>
+        <v>10.26</v>
       </c>
       <c r="AD8">
-        <v>18.41</v>
+        <v>4.84</v>
       </c>
       <c r="AE8">
-        <v>38.81</v>
+        <v>95.45</v>
       </c>
       <c r="AF8">
-        <v>605.26</v>
+        <v>4.76</v>
       </c>
       <c r="AG8">
-        <v>-69.34999999999999</v>
+        <v>-46.15</v>
       </c>
       <c r="AH8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AI8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="AK8">
-        <v>19.30665599426579</v>
+        <v>47.74710202901668</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1484,43 +1505,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>93.75</v>
+        <v>98.79032258064517</v>
       </c>
       <c r="C9">
-        <v>479</v>
+        <v>347</v>
       </c>
       <c r="D9">
-        <v>539.84</v>
+        <v>241.86</v>
       </c>
       <c r="E9">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="F9">
-        <v>-0.7431907280374098</v>
+        <v>0.2218257809200236</v>
       </c>
       <c r="G9">
-        <v>1.52</v>
+        <v>2.33</v>
       </c>
       <c r="H9">
-        <v>-0.8593107068477105</v>
+        <v>0.3375475478558731</v>
       </c>
       <c r="I9">
-        <v>540.560009765625</v>
+        <v>239.7619995117188</v>
       </c>
       <c r="J9">
-        <v>518.2660049438476</v>
+        <v>231.4369987487793</v>
       </c>
       <c r="K9">
-        <v>502.2216027832031</v>
+        <v>204.7711993408203</v>
       </c>
       <c r="L9">
-        <v>423.1370502471924</v>
+        <v>168.4881498336792</v>
       </c>
       <c r="M9">
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1529,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1547,46 +1568,46 @@
         <v>1</v>
       </c>
       <c r="X9">
-        <v>246.83</v>
+        <v>79.06</v>
       </c>
       <c r="Y9">
-        <v>547.8</v>
+        <v>248.71</v>
       </c>
       <c r="Z9">
-        <v>26.18</v>
+        <v>19.78</v>
       </c>
       <c r="AA9">
-        <v>-15.19</v>
+        <v>19.49</v>
       </c>
       <c r="AB9">
-        <v>4.88</v>
+        <v>22.57</v>
       </c>
       <c r="AC9">
-        <v>127.81</v>
+        <v>294.57</v>
       </c>
       <c r="AD9">
-        <v>9.460000000000001</v>
+        <v>7.01</v>
       </c>
       <c r="AE9">
-        <v>14.52</v>
+        <v>327.06</v>
       </c>
       <c r="AF9">
-        <v>70.64</v>
+        <v>7.59</v>
       </c>
       <c r="AG9">
-        <v>16.58</v>
+        <v>-14.13</v>
       </c>
       <c r="AH9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="AI9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AJ9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AK9">
-        <v>15.59576406332494</v>
+        <v>46.06094383337521</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1594,58 +1615,61 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>91.33064516129032</v>
+        <v>98.38709677419355</v>
       </c>
       <c r="C10">
-        <v>135</v>
+        <v>397</v>
       </c>
       <c r="D10">
-        <v>48.05</v>
+        <v>453.75</v>
       </c>
       <c r="E10">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="F10">
-        <v>-0.6046297448439942</v>
+        <v>0.006721993361212836</v>
       </c>
       <c r="G10">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="H10">
-        <v>-0.9579875344283089</v>
+        <v>-0.1253748034893248</v>
       </c>
       <c r="I10">
-        <v>48.46399993896485</v>
+        <v>445.0300048828125</v>
       </c>
       <c r="J10">
-        <v>47.1144998550415</v>
+        <v>421.1759994506836</v>
       </c>
       <c r="K10">
-        <v>45.59660003662109</v>
+        <v>423.7588000488281</v>
       </c>
       <c r="L10">
-        <v>39.78779994010925</v>
+        <v>326.1811990356445</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
-        <v>1.06</v>
+        <v>1.05</v>
+      </c>
+      <c r="O10" t="s">
+        <v>52</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="U10" t="b">
         <v>0</v>
@@ -1654,49 +1678,49 @@
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>23.26</v>
+        <v>169.34</v>
       </c>
       <c r="Y10">
-        <v>49.1</v>
+        <v>458.57</v>
       </c>
       <c r="Z10">
-        <v>37.57</v>
+        <v>26.61</v>
       </c>
       <c r="AA10">
-        <v>0.21</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="AB10">
-        <v>9.619999999999999</v>
+        <v>40.71</v>
       </c>
       <c r="AC10">
-        <v>46.67</v>
+        <v>10.75</v>
       </c>
       <c r="AD10">
-        <v>5.75</v>
+        <v>7.72</v>
       </c>
       <c r="AE10">
-        <v>-56.86</v>
+        <v>-13.81</v>
       </c>
       <c r="AF10">
-        <v>18.6</v>
+        <v>18.32</v>
       </c>
       <c r="AG10">
-        <v>186.67</v>
+        <v>8.6</v>
       </c>
       <c r="AH10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AI10" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AJ10" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AK10">
-        <v>14.53986279214808</v>
+        <v>37.68438216783113</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1704,46 +1728,46 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>95.56451612903226</v>
+        <v>95.76612903225806</v>
       </c>
       <c r="C11">
-        <v>333</v>
+        <v>488</v>
       </c>
       <c r="D11">
-        <v>214.05</v>
+        <v>590.6</v>
       </c>
       <c r="E11">
-        <v>1.52</v>
+        <v>0.89</v>
       </c>
       <c r="F11">
-        <v>-0.4030864965626628</v>
+        <v>-0.6856433228437088</v>
       </c>
       <c r="G11">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="H11">
-        <v>-1.068998965456482</v>
+        <v>-0.6943835270177972</v>
       </c>
       <c r="I11">
-        <v>214.5</v>
+        <v>586.7160034179688</v>
       </c>
       <c r="J11">
-        <v>209.1354995727539</v>
+        <v>575.4609985351562</v>
       </c>
       <c r="K11">
-        <v>208.717399597168</v>
+        <v>553.6415966796875</v>
       </c>
       <c r="L11">
-        <v>174.3391500091553</v>
+        <v>477.0145993041992</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -1755,58 +1779,58 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="U11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>92.06</v>
+        <v>246.83</v>
       </c>
       <c r="Y11">
-        <v>217.42</v>
+        <v>594.77</v>
       </c>
       <c r="Z11">
-        <v>64.66</v>
+        <v>28.54</v>
       </c>
       <c r="AA11">
-        <v>5.27</v>
+        <v>-17.05</v>
       </c>
       <c r="AB11">
-        <v>11.76</v>
+        <v>25.42</v>
       </c>
       <c r="AC11">
-        <v>31.56</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="AD11">
-        <v>63.66</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>-3.76</v>
       </c>
       <c r="AF11">
-        <v>113.71</v>
+        <v>14.52</v>
       </c>
       <c r="AG11">
-        <v>-38.44</v>
+        <v>70.64</v>
       </c>
       <c r="AH11" t="s">
         <v>55</v>
       </c>
       <c r="AI11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="AK11">
-        <v>13.53668685050874</v>
+        <v>37.45221108752275</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1814,109 +1838,109 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>96.57258064516128</v>
+        <v>90.7258064516129</v>
       </c>
       <c r="C12">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="D12">
-        <v>43.31</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="E12">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="F12">
-        <v>0.7054013689846603</v>
+        <v>0.1209958805018309</v>
       </c>
       <c r="G12">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="H12">
-        <v>0.4111534482524926</v>
+        <v>-0.0867979408772251</v>
       </c>
       <c r="I12">
-        <v>44.00199966430664</v>
+        <v>88.28799896240234</v>
       </c>
       <c r="J12">
-        <v>45.32049999237061</v>
+        <v>89.26149902343749</v>
       </c>
       <c r="K12">
-        <v>41.48479995727539</v>
+        <v>87.96519958496094</v>
       </c>
       <c r="L12">
-        <v>30.02359995365143</v>
+        <v>79.13285003662109</v>
       </c>
       <c r="M12">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="N12">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>6.111111111111111</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
       </c>
       <c r="X12">
-        <v>13.08</v>
+        <v>45.25</v>
       </c>
       <c r="Y12">
-        <v>49.2</v>
+        <v>106.22</v>
       </c>
       <c r="Z12">
-        <v>8.720000000000001</v>
+        <v>21.54</v>
       </c>
       <c r="AA12">
-        <v>44.34</v>
+        <v>56.21</v>
       </c>
       <c r="AB12">
-        <v>110.32</v>
+        <v>15.53</v>
       </c>
       <c r="AC12">
-        <v>157.14</v>
+        <v>133.33</v>
       </c>
       <c r="AD12">
-        <v>4.13</v>
+        <v>76.39</v>
       </c>
       <c r="AE12">
-        <v>1900</v>
+        <v>43.97</v>
       </c>
       <c r="AF12">
-        <v>-118.75</v>
+        <v>25.89</v>
       </c>
       <c r="AG12">
-        <v>-23.81</v>
+        <v>28.74</v>
       </c>
       <c r="AH12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="AK12">
-        <v>62.0751937050712</v>
+        <v>36.2991208465325</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1924,49 +1948,49 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>90.92741935483872</v>
+        <v>92.74193548387096</v>
       </c>
       <c r="C13">
-        <v>217</v>
+        <v>465</v>
       </c>
       <c r="D13">
-        <v>63.95</v>
+        <v>423.4</v>
       </c>
       <c r="E13">
-        <v>2.07</v>
+        <v>0.72</v>
       </c>
       <c r="F13">
-        <v>0.289718419404414</v>
+        <v>-0.7999172099843268</v>
       </c>
       <c r="G13">
-        <v>2.29</v>
+        <v>0.96</v>
       </c>
       <c r="H13">
-        <v>0.09045375861554836</v>
+        <v>-0.9837099966085459</v>
       </c>
       <c r="I13">
-        <v>64.80533370971679</v>
+        <v>417.5699951171875</v>
       </c>
       <c r="J13">
-        <v>59.77499980926514</v>
+        <v>406.4839965820312</v>
       </c>
       <c r="K13">
-        <v>57.32129981994629</v>
+        <v>385.6857983398438</v>
       </c>
       <c r="L13">
-        <v>51.12989156723022</v>
+        <v>308.3546997833252</v>
       </c>
       <c r="M13">
+        <v>1.03</v>
+      </c>
+      <c r="N13">
         <v>1.08</v>
       </c>
-      <c r="N13">
-        <v>1.13</v>
-      </c>
       <c r="P13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1975,58 +1999,388 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>1.111111111111111</v>
+        <v>4.444444444444444</v>
       </c>
       <c r="U13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
       </c>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>30.7</v>
+        <v>187.31</v>
       </c>
       <c r="Y13">
-        <v>66.04000000000001</v>
+        <v>424.69</v>
       </c>
       <c r="Z13">
-        <v>9.390000000000001</v>
+        <v>21.48</v>
       </c>
       <c r="AA13">
-        <v>444</v>
+        <v>3.73</v>
       </c>
       <c r="AB13">
-        <v>44.34</v>
+        <v>6.18</v>
       </c>
       <c r="AC13">
-        <v>531.91</v>
+        <v>32.84</v>
       </c>
       <c r="AD13">
-        <v>2.32</v>
+        <v>62.36</v>
       </c>
       <c r="AE13">
-        <v>-86.69</v>
+        <v>13.87</v>
       </c>
       <c r="AF13">
-        <v>151.12</v>
+        <v>-32.39</v>
       </c>
       <c r="AG13">
-        <v>1391.86</v>
+        <v>72.55</v>
       </c>
       <c r="AH13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AI13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AJ13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AK13">
-        <v>57.82604093989458</v>
+        <v>18.84091559887381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14">
+        <v>90.32258064516128</v>
+      </c>
+      <c r="C14">
+        <v>456</v>
+      </c>
+      <c r="D14">
+        <v>225.73</v>
+      </c>
+      <c r="E14">
+        <v>0.89</v>
+      </c>
+      <c r="F14">
+        <v>-0.6856433228437088</v>
+      </c>
+      <c r="G14">
+        <v>1.1</v>
+      </c>
+      <c r="H14">
+        <v>-0.8486909774661964</v>
+      </c>
+      <c r="I14">
+        <v>226.2499969482422</v>
+      </c>
+      <c r="J14">
+        <v>220.4869987487793</v>
+      </c>
+      <c r="K14">
+        <v>212.9657989501953</v>
+      </c>
+      <c r="L14">
+        <v>190.0183993530273</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>1.06</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>113.56</v>
+      </c>
+      <c r="Y14">
+        <v>228.88</v>
+      </c>
+      <c r="Z14">
+        <v>17.62</v>
+      </c>
+      <c r="AA14">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="AB14">
+        <v>10.1</v>
+      </c>
+      <c r="AC14">
+        <v>22.78</v>
+      </c>
+      <c r="AD14">
+        <v>10.79</v>
+      </c>
+      <c r="AE14">
+        <v>-12.3</v>
+      </c>
+      <c r="AF14">
+        <v>9.57</v>
+      </c>
+      <c r="AG14">
+        <v>27.78</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK14">
+        <v>18.37948557899692</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>91.73387096774194</v>
+      </c>
+      <c r="C15">
+        <v>70</v>
+      </c>
+      <c r="D15">
+        <v>104.25</v>
+      </c>
+      <c r="E15">
+        <v>1.05</v>
+      </c>
+      <c r="F15">
+        <v>-0.5780914290643033</v>
+      </c>
+      <c r="G15">
+        <v>1.58</v>
+      </c>
+      <c r="H15">
+        <v>-0.3857686261209985</v>
+      </c>
+      <c r="I15">
+        <v>104.381999206543</v>
+      </c>
+      <c r="J15">
+        <v>103.2024997711182</v>
+      </c>
+      <c r="K15">
+        <v>97.25080001831054</v>
+      </c>
+      <c r="L15">
+        <v>82.53924993515015</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>1.07</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>45.86</v>
+      </c>
+      <c r="Y15">
+        <v>105.81</v>
+      </c>
+      <c r="Z15">
+        <v>168.8</v>
+      </c>
+      <c r="AA15">
+        <v>16.45</v>
+      </c>
+      <c r="AB15">
+        <v>4.94</v>
+      </c>
+      <c r="AC15">
+        <v>11.9</v>
+      </c>
+      <c r="AD15">
+        <v>3.5</v>
+      </c>
+      <c r="AE15">
+        <v>-15.32</v>
+      </c>
+      <c r="AF15">
+        <v>18.72</v>
+      </c>
+      <c r="AG15">
+        <v>11.31</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK15">
+        <v>7.283954806941703</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16">
+        <v>92.13709677419355</v>
+      </c>
+      <c r="C16">
+        <v>476</v>
+      </c>
+      <c r="D16">
+        <v>643.39</v>
+      </c>
+      <c r="E16">
+        <v>1.04</v>
+      </c>
+      <c r="F16">
+        <v>-0.5848134224255161</v>
+      </c>
+      <c r="G16">
+        <v>1.16</v>
+      </c>
+      <c r="H16">
+        <v>-0.7908256835480468</v>
+      </c>
+      <c r="I16">
+        <v>635.3739990234375</v>
+      </c>
+      <c r="J16">
+        <v>622.1024963378907</v>
+      </c>
+      <c r="K16">
+        <v>574.241000366211</v>
+      </c>
+      <c r="L16">
+        <v>442.6185997009277</v>
+      </c>
+      <c r="M16">
+        <v>1.02</v>
+      </c>
+      <c r="N16">
+        <v>1.11</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U16" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>301.67</v>
+      </c>
+      <c r="Y16">
+        <v>644.14</v>
+      </c>
+      <c r="Z16">
+        <v>30.15</v>
+      </c>
+      <c r="AA16">
+        <v>22.69</v>
+      </c>
+      <c r="AB16">
+        <v>2.31</v>
+      </c>
+      <c r="AC16">
+        <v>26.87</v>
+      </c>
+      <c r="AD16">
+        <v>5.18</v>
+      </c>
+      <c r="AE16">
+        <v>4.64</v>
+      </c>
+      <c r="AF16">
+        <v>27.63</v>
+      </c>
+      <c r="AG16">
+        <v>-5</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK16">
+        <v>6.76245321329035</v>
       </c>
     </row>
   </sheetData>
